--- a/artfynd/A 39250-2024 artfynd.xlsx
+++ b/artfynd/A 39250-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120496204</v>
+        <v>120496234</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>90600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549221</v>
+        <v>549172</v>
       </c>
       <c r="R3" t="n">
-        <v>6664303</v>
+        <v>6664319</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120496234</v>
+        <v>120496204</v>
       </c>
       <c r="B4" t="n">
-        <v>90600</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549172</v>
+        <v>549221</v>
       </c>
       <c r="R4" t="n">
-        <v>6664319</v>
+        <v>6664303</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 39250-2024 artfynd.xlsx
+++ b/artfynd/A 39250-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120496110</v>
+        <v>120496204</v>
       </c>
       <c r="B2" t="n">
         <v>91881</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Paddtjärnsflytet, Paddtjärnsflytet, Vstm</t>
+          <t>Paddtjärnen, Paddtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549182</v>
+        <v>549221</v>
       </c>
       <c r="R2" t="n">
-        <v>6664441</v>
+        <v>6664303</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120496234</v>
+        <v>120496110</v>
       </c>
       <c r="B3" t="n">
-        <v>90600</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Paddtjärnen, Paddtjärnen, Vstm</t>
+          <t>Paddtjärnsflytet, Paddtjärnsflytet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549172</v>
+        <v>549182</v>
       </c>
       <c r="R3" t="n">
-        <v>6664319</v>
+        <v>6664441</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120496204</v>
+        <v>120496234</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>90600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549221</v>
+        <v>549172</v>
       </c>
       <c r="R4" t="n">
-        <v>6664303</v>
+        <v>6664319</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
